--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>103749868</v>
       </c>
       <c r="B3" t="n">
-        <v>90207</v>
+        <v>90217</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>103749868</v>
       </c>
       <c r="B3" t="n">
-        <v>90217</v>
+        <v>90229</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>103749868</v>
       </c>
       <c r="B3" t="n">
-        <v>90229</v>
+        <v>90230</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>103749868</v>
       </c>
       <c r="B3" t="n">
-        <v>90230</v>
+        <v>90233</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>103749868</v>
       </c>
       <c r="B3" t="n">
-        <v>90233</v>
+        <v>90239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103758266</v>
+        <v>103749956</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2671</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +710,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>V Roslagsleden, Domarudden, Upl</t>
+          <t>Roslagsleden V, Domarudden, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>688678.4010888282</v>
+        <v>688538</v>
       </c>
       <c r="R2" t="n">
-        <v>6604573.873461153</v>
+        <v>6604620</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,57 +773,57 @@
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103749868</v>
+        <v>103758266</v>
       </c>
       <c r="B3" t="n">
-        <v>90239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Dialog hos rapportör</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>256335</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Milspåret, Domarudden, Upl</t>
+          <t>V Roslagsleden, Domarudden, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>688631</v>
+        <v>688678</v>
       </c>
       <c r="R3" t="n">
-        <v>6604582</v>
+        <v>6604573</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -894,62 +879,52 @@
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103749956</v>
+        <v>103749868</v>
       </c>
       <c r="B4" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2671</v>
+        <v>256335</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Roslagsleden V, Domarudden, Upl</t>
+          <t>Milspåret, Domarudden, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>688538.6694180608</v>
+        <v>688631</v>
       </c>
       <c r="R4" t="n">
-        <v>6604620.195727034</v>
+        <v>6604582</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -979,19 +954,9 @@
           <t>2022-09-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 12620-2022 artfynd.xlsx
+++ b/artfynd/A 12620-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103749956</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103758266</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,8 +1000,18 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103749868</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>